--- a/报关资料模板（有多个商品）.xlsx
+++ b/报关资料模板（有多个商品）.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="21600" windowHeight="9555" activeTab="1"/>
+    <workbookView windowWidth="21600" windowHeight="9555" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet name="委托书" sheetId="5" r:id="rId1"/>
@@ -2671,6 +2671,13 @@
     </font>
     <font>
       <b/>
+      <sz val="12"/>
+      <color indexed="10"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
       <sz val="24"/>
       <name val="Times New Roman"/>
       <charset val="0"/>
@@ -2687,13 +2694,6 @@
       <sz val="20"/>
       <name val="Times New Roman"/>
       <charset val="0"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="12"/>
-      <color indexed="10"/>
-      <name val="宋体"/>
-      <charset val="134"/>
     </font>
   </fonts>
   <fills count="38">
@@ -13515,7 +13515,7 @@
       </c>
       <c r="H23" s="343">
         <f ca="1">TODAY()</f>
-        <v>46160</v>
+        <v>46167</v>
       </c>
       <c r="I23" s="343"/>
       <c r="J23" s="343"/>
@@ -13551,7 +13551,7 @@
       </c>
       <c r="C25" s="348">
         <f ca="1">报关单!L3</f>
-        <v>46160</v>
+        <v>46167</v>
       </c>
       <c r="D25" s="349"/>
       <c r="E25" s="348"/>
@@ -13804,7 +13804,7 @@
       <c r="D45" s="381"/>
       <c r="E45" s="382">
         <f ca="1">TODAY()-1</f>
-        <v>46159</v>
+        <v>46166</v>
       </c>
       <c r="G45" s="361" t="s">
         <v>41</v>
@@ -13812,7 +13812,7 @@
       <c r="H45" s="383"/>
       <c r="I45" s="384">
         <f ca="1">TODAY()</f>
-        <v>46160</v>
+        <v>46167</v>
       </c>
       <c r="J45" s="385"/>
     </row>
@@ -13991,7 +13991,7 @@
       </c>
       <c r="L3" s="205">
         <f ca="1">委托书!I45</f>
-        <v>46160</v>
+        <v>46167</v>
       </c>
       <c r="M3" s="199"/>
       <c r="N3" s="200"/>
@@ -17075,7 +17075,7 @@
       </c>
       <c r="G4" s="168">
         <f ca="1">TODAY()</f>
-        <v>46160</v>
+        <v>46167</v>
       </c>
       <c r="H4" s="169"/>
     </row>
@@ -17182,7 +17182,7 @@
         <v>个</v>
       </c>
       <c r="F10" s="177">
-        <f ca="1" t="shared" ref="F10:F22" si="0">IFERROR(H10/D10,0)</f>
+        <f ca="1">IFERROR(H10/D10,0)</f>
         <v>0.1075</v>
       </c>
       <c r="G10" s="178" t="str">
@@ -17210,7 +17210,7 @@
         <v>个</v>
       </c>
       <c r="F11" s="177">
-        <f ca="1" t="shared" si="0"/>
+        <f ca="1">IFERROR(H11/D11,0)</f>
         <v>0.12</v>
       </c>
       <c r="G11" s="178" t="str">
@@ -17238,7 +17238,7 @@
         <v>个</v>
       </c>
       <c r="F12" s="177">
-        <f ca="1" t="shared" si="0"/>
+        <f ca="1">IFERROR(H12/D12,0)</f>
         <v>0.12</v>
       </c>
       <c r="G12" s="178" t="str">
@@ -17266,7 +17266,7 @@
         <v>个</v>
       </c>
       <c r="F13" s="177">
-        <f ca="1" t="shared" si="0"/>
+        <f ca="1">IFERROR(H13/D13,0)</f>
         <v>0.06</v>
       </c>
       <c r="G13" s="178" t="str">
@@ -17294,7 +17294,7 @@
         <v>0</v>
       </c>
       <c r="F14" s="177">
-        <f ca="1" t="shared" si="0"/>
+        <f ca="1" t="shared" ref="F14:F22" si="0">IFERROR(H14/D14,0)</f>
         <v>0</v>
       </c>
       <c r="G14" s="178">
@@ -17430,7 +17430,7 @@
         <v>0</v>
       </c>
       <c r="E19" s="176">
-        <f ca="1">OFFSET(报关单!$H$1,ROW(报关单!H12)*3+18,0)</f>
+        <f ca="1">OFFSET(报关单!$H$1,ROW(报关单!H11)*3+18,0)</f>
         <v>0</v>
       </c>
       <c r="F19" s="177">
@@ -17450,15 +17450,15 @@
       <c r="A20" s="173"/>
       <c r="B20" s="174"/>
       <c r="C20" s="175">
-        <f ca="1">OFFSET(报关单!$D$1,ROW(报关单!D13)*3+16,0)</f>
+        <f ca="1">OFFSET(报关单!$D$1,ROW(报关单!D12)*3+16,0)</f>
         <v>0</v>
       </c>
       <c r="D20" s="175">
-        <f ca="1">OFFSET(报关单!$G$1,ROW(报关单!G13)*3+18,0)</f>
+        <f ca="1">OFFSET(报关单!$G$1,ROW(报关单!G12)*3+18,0)</f>
         <v>0</v>
       </c>
       <c r="E20" s="176">
-        <f ca="1">OFFSET(报关单!$H$1,ROW(报关单!H13)*3+18,0)</f>
+        <f ca="1">OFFSET(报关单!$H$1,ROW(报关单!H12)*3+18,0)</f>
         <v>0</v>
       </c>
       <c r="F20" s="177">
@@ -17478,15 +17478,15 @@
       <c r="A21" s="173"/>
       <c r="B21" s="174"/>
       <c r="C21" s="175">
-        <f ca="1">OFFSET(报关单!$D$1,ROW(报关单!D14)*3+16,0)</f>
+        <f ca="1">OFFSET(报关单!$D$1,ROW(报关单!D13)*3+16,0)</f>
         <v>0</v>
       </c>
       <c r="D21" s="175">
-        <f ca="1">OFFSET(报关单!$G$1,ROW(报关单!G14)*3+18,0)</f>
+        <f ca="1">OFFSET(报关单!$G$1,ROW(报关单!G13)*3+18,0)</f>
         <v>0</v>
       </c>
       <c r="E21" s="176">
-        <f ca="1">OFFSET(报关单!$H$1,ROW(报关单!H14)*3+18,0)</f>
+        <f ca="1">OFFSET(报关单!$H$1,ROW(报关单!H13)*3+18,0)</f>
         <v>0</v>
       </c>
       <c r="F21" s="177">
@@ -17494,11 +17494,11 @@
         <v>0</v>
       </c>
       <c r="G21" s="178">
-        <f ca="1">OFFSET(报关单!$I$1,ROW(报关单!I14)*3+18,0)</f>
+        <f ca="1">OFFSET(报关单!$I$1,ROW(报关单!I13)*3+18,0)</f>
         <v>0</v>
       </c>
       <c r="H21" s="177">
-        <f ca="1">OFFSET(报关单!$I$1,ROW(报关单!I14)*3+17,0)</f>
+        <f ca="1">OFFSET(报关单!$I$1,ROW(报关单!I13)*3+17,0)</f>
         <v>0</v>
       </c>
     </row>
@@ -17506,15 +17506,15 @@
       <c r="A22" s="173"/>
       <c r="B22" s="174"/>
       <c r="C22" s="175">
-        <f ca="1">OFFSET(报关单!$D$1,ROW(报关单!D15)*3+16,0)</f>
+        <f ca="1">OFFSET(报关单!$D$1,ROW(报关单!D14)*3+16,0)</f>
         <v>0</v>
       </c>
       <c r="D22" s="175">
-        <f ca="1">OFFSET(报关单!$G$1,ROW(报关单!G15)*3+18,0)</f>
+        <f ca="1">OFFSET(报关单!$G$1,ROW(报关单!G14)*3+18,0)</f>
         <v>0</v>
       </c>
       <c r="E22" s="176">
-        <f ca="1">OFFSET(报关单!$H$1,ROW(报关单!H15)*3+18,0)</f>
+        <f ca="1">OFFSET(报关单!$H$1,ROW(报关单!H14)*3+18,0)</f>
         <v>0</v>
       </c>
       <c r="F22" s="177">
@@ -17522,11 +17522,11 @@
         <v>0</v>
       </c>
       <c r="G22" s="178">
-        <f ca="1">OFFSET(报关单!$I$1,ROW(报关单!I15)*3+18,0)</f>
+        <f ca="1">OFFSET(报关单!$I$1,ROW(报关单!I14)*3+18,0)</f>
         <v>0</v>
       </c>
       <c r="H22" s="177">
-        <f ca="1">OFFSET(报关单!$I$1,ROW(报关单!I15)*3+17,0)</f>
+        <f ca="1">OFFSET(报关单!$I$1,ROW(报关单!I14)*3+17,0)</f>
         <v>0</v>
       </c>
     </row>
@@ -18035,7 +18035,7 @@
       </c>
       <c r="G9" s="85">
         <f ca="1">报关单!L3</f>
-        <v>46160</v>
+        <v>46167</v>
       </c>
       <c r="H9" s="85"/>
       <c r="I9" s="85"/>
@@ -18763,7 +18763,7 @@
       </c>
       <c r="C44" s="139">
         <f ca="1">TODAY()+30</f>
-        <v>46190</v>
+        <v>46197</v>
       </c>
       <c r="D44" s="139"/>
       <c r="E44" s="140" t="s">
@@ -19096,7 +19096,7 @@
       </c>
       <c r="G3" s="14">
         <f ca="1">报关单!L3</f>
-        <v>46160</v>
+        <v>46167</v>
       </c>
     </row>
     <row r="4" s="5" customFormat="1" ht="30" customHeight="1" spans="1:21">
@@ -19301,7 +19301,10 @@
         <f ca="1">发票!D11</f>
         <v>2000</v>
       </c>
-      <c r="E12" s="50"/>
+      <c r="E12" s="50" t="str">
+        <f ca="1">发票!E11</f>
+        <v>个</v>
+      </c>
       <c r="F12" s="51">
         <f>C12*10</f>
         <v>20</v>
@@ -19333,7 +19336,10 @@
         <f ca="1">发票!D12</f>
         <v>2000</v>
       </c>
-      <c r="E13" s="50"/>
+      <c r="E13" s="50" t="str">
+        <f ca="1">发票!E12</f>
+        <v>个</v>
+      </c>
       <c r="F13" s="51">
         <f>C13*5.9</f>
         <v>11.8</v>
@@ -19357,7 +19363,10 @@
         <f ca="1">发票!D13</f>
         <v>3000</v>
       </c>
-      <c r="E14" s="50"/>
+      <c r="E14" s="50" t="str">
+        <f ca="1">发票!E13</f>
+        <v>个</v>
+      </c>
       <c r="F14" s="51">
         <f>15</f>
         <v>15</v>
@@ -19379,7 +19388,10 @@
       </c>
       <c r="C15" s="48"/>
       <c r="D15" s="49"/>
-      <c r="E15" s="50"/>
+      <c r="E15" s="50">
+        <f ca="1">发票!E14</f>
+        <v>0</v>
+      </c>
       <c r="F15" s="51"/>
       <c r="G15" s="48"/>
       <c r="H15" s="52"/>
@@ -19395,7 +19407,10 @@
         <f ca="1">发票!D15</f>
         <v>0</v>
       </c>
-      <c r="E16" s="50"/>
+      <c r="E16" s="50">
+        <f ca="1">发票!E15</f>
+        <v>0</v>
+      </c>
       <c r="F16" s="51"/>
       <c r="G16" s="48">
         <f>F16-C16</f>

--- a/报关资料模板（有多个商品）.xlsx
+++ b/报关资料模板（有多个商品）.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="21600" windowHeight="9555" activeTab="5"/>
+    <workbookView windowWidth="21600" windowHeight="9555" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="委托书" sheetId="5" r:id="rId1"/>
